--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-binary.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-binary.xlsx
@@ -433,7 +433,7 @@
     <t>Binary.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -471,7 +471,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -529,7 +529,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -559,7 +559,7 @@
     <t>Binary.securityContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -918,7 +918,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -933,7 +933,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="88.5703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="35.8125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
